--- a/AAII_Financials/Yearly/STWD_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/STWD_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="92">
   <si>
     <t>STWD</t>
   </si>
@@ -656,197 +656,209 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40908</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2341200</v>
+      </c>
+      <c r="E8" s="3">
         <v>2220500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1176500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1136200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1196400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1109300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>879900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>784700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>735900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>702900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>549500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>307300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>206500</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1559600</v>
+      </c>
+      <c r="E9" s="3">
         <v>934000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>593400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>528900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>607600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>525100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>407900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>348300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>327300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>278800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>188600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>104400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>68000</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>781500</v>
+      </c>
+      <c r="E10" s="3">
         <v>1286500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>583100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>607300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>588800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>584200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>471900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>436400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>408600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>424000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>360900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>202900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>138500</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -863,8 +875,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -904,9 +917,12 @@
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -946,93 +962,102 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>127100</v>
+      </c>
+      <c r="E14" s="3">
         <v>4600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>8600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>7200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>21300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>14800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>10600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>22300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>19400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>5500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>23700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>10700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>11000</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>49100</v>
+      </c>
+      <c r="E15" s="3">
         <v>49300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>83000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>94400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>113300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>132600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>93600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>66800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>29000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>16600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>9700</v>
       </c>
-      <c r="N15" s="3">
-        <v>0</v>
-      </c>
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1046,92 +1071,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2224500</v>
+      </c>
+      <c r="E17" s="3">
         <v>1274100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>996500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>968100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1048800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>983400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>741300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>660000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>542200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>485800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>375200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>129000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>87700</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>116700</v>
+      </c>
+      <c r="E18" s="3">
         <v>946300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>180000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>168100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>147600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>125800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>138500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>124700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>193700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>217100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>174300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>178300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>118700</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1148,92 +1180,99 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>300800</v>
+      </c>
+      <c r="E20" s="3">
         <v>51200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>321100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>218200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>402600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>300700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>305700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>251300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>275700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>309100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>179700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>28300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>2700</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>471800</v>
+      </c>
+      <c r="E21" s="3">
         <v>1051500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>585700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>480400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>663600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>557400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>535200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>437600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>496600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>542800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>368900</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1273,93 +1312,102 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>417500</v>
+      </c>
+      <c r="E23" s="3">
         <v>997500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>501100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>386300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>550200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>426500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>444300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>376000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>469400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>526200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>354000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>206600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>121400</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E24" s="3">
         <v>-61500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>8700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>20200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>13200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>15300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>21200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>8300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>17200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>24100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>23900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>800</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1399,93 +1447,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>418200</v>
+      </c>
+      <c r="E26" s="3">
         <v>1059100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>492400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>366100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>536900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>411200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>423100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>367700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>452200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>502100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>330100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>205700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>120600</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>332800</v>
+      </c>
+      <c r="E27" s="3">
         <v>854400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>440900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>326500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>505800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>382200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>408000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>363100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>447300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>491000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>323200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>201600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>117200</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1525,9 +1582,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1540,36 +1600,39 @@
       <c r="F29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G29" s="3">
-        <v>0</v>
+      <c r="G29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H29" s="3">
         <v>0</v>
       </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>-10400</v>
       </c>
-      <c r="J29" s="3">
-        <v>0</v>
-      </c>
       <c r="K29" s="3">
         <v>0</v>
       </c>
       <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
         <v>-1600</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-19800</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-2000</v>
       </c>
-      <c r="O29" s="3" t="s">
+      <c r="P29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1609,9 +1672,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1651,93 +1717,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-300800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-51200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-321100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-218200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-402600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-300700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-305700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-251300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-275700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-309100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-179700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-28300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-2700</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>332800</v>
+      </c>
+      <c r="E33" s="3">
         <v>854400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>440900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>326500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>505800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>382200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>397600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>363100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>447300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>489400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>303500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>199600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>117200</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1777,98 +1852,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>332800</v>
+      </c>
+      <c r="E35" s="3">
         <v>854400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>440900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>326500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>505800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>382200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>397600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>363100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>447300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>489400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>303500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>199600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>117200</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40908</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1885,8 +1969,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1903,50 +1988,54 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>194700</v>
+      </c>
+      <c r="E41" s="3">
         <v>261100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>217400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>563200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>478400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>239800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>369400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>615500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>368800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>255200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>317600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>177700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>114000</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1986,51 +2075,57 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>200900</v>
+      </c>
+      <c r="E43" s="3">
         <v>168500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>116300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>96000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>64100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>60400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>47700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>28200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>34300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>40100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>37600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>24100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>15200</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2070,9 +2165,12 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2112,9 +2210,12 @@
       <c r="O45" s="3">
         <v>0</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2154,80 +2255,86 @@
       <c r="O46" s="3">
         <v>0</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P46" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>21045800</v>
+      </c>
+      <c r="E47" s="3">
         <v>22093700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>19364700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>12984600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>12364800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>10872500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>8286300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>6958500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>7187700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>7492500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>6773400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>4084900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2833600</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3059200</v>
+      </c>
+      <c r="E48" s="3">
         <v>3211000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2206700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2271200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2266400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2784900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2647500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1944700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>919200</v>
-      </c>
-      <c r="L48" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M48" s="3" t="s">
         <v>8</v>
@@ -2238,51 +2345,57 @@
       <c r="O48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>324800</v>
+      </c>
+      <c r="E49" s="3">
         <v>328600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>323400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>330000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>345500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>404900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>323500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>359700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>342000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>284600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>317600</v>
-      </c>
-      <c r="N49" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2322,9 +2435,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2364,51 +2480,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>117300</v>
+      </c>
+      <c r="E52" s="3">
         <v>121100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>104600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>161900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>109700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>266200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>48800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>35200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>23100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>48700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>69100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3400</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
-      </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2448,51 +2570,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>69504200</v>
+      </c>
+      <c r="E54" s="3">
         <v>79043100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>83850400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>80873500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>78042300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>68262500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>62941300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>77256300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>85698400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>116099000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>110771000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4324400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2997400</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2509,8 +2637,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2527,73 +2656,77 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>293400</v>
+      </c>
+      <c r="E57" s="3">
         <v>299000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>189700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>206800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>212000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>217700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>185100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>198100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>156800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>144500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>225400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>8900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>13400</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1326200</v>
+      </c>
+      <c r="E58" s="3">
         <v>1874300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2068300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>656700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>480200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>565200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>572900</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>8</v>
@@ -2610,51 +2743,57 @@
       <c r="O58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>197700</v>
+      </c>
+      <c r="E59" s="3">
         <v>192700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>224000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>177100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>178400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>177500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>168300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>162900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>155900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>148900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>108000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>75600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>41400</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2694,51 +2833,57 @@
       <c r="O60" s="3">
         <v>0</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P60" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>18385600</v>
+      </c>
+      <c r="E61" s="3">
         <v>18632700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>14953300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>12152500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>11282500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>10191400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>7399600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>6200700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5392500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4685300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3436600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1393700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1156700</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2778,9 +2923,12 @@
       <c r="O62" s="3">
         <v>0</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2820,9 +2968,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2862,9 +3013,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2904,51 +3058,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>63253100</v>
+      </c>
+      <c r="E66" s="3">
         <v>72580700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>77777900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>76384600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>73341900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>63659000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>58462900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>72734000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>81558000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>112238000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>106488000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1605000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1238000</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2965,8 +3125,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3006,9 +3167,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3048,9 +3212,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3090,9 +3257,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3132,51 +3302,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>505900</v>
+      </c>
+      <c r="E72" s="3">
         <v>769200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>493100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-629700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-381700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-349000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-217300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-115600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-12300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-9400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-84700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-72400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-55100</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3216,9 +3392,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3258,9 +3437,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3300,51 +3482,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6251100</v>
+      </c>
+      <c r="E76" s="3">
         <v>6462400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>6072500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4488900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4700400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4603400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4478400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4522300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4140300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3860900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4282500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2719300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1759500</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3384,98 +3572,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40908</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>332800</v>
+      </c>
+      <c r="E81" s="3">
         <v>854400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>440900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>326500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>505800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>382200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>397600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>363100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>447300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>489400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>303500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>199600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>117200</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3492,50 +3689,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>54300</v>
+      </c>
+      <c r="E83" s="3">
         <v>53900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>84600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>94200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>113400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>130800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>90900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>61600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>27200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>16600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>14900</v>
-      </c>
-      <c r="N83" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3575,9 +3776,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3617,9 +3821,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3659,9 +3866,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3701,9 +3911,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3743,51 +3956,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>528600</v>
+      </c>
+      <c r="E89" s="3">
         <v>213700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-990000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1045500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-13200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>585500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-246800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>556600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>605700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>220700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>326300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>265600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>79400</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3804,8 +4023,9 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3813,10 +4033,10 @@
         <v>0</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-28100</v>
-      </c>
-      <c r="F91" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G91" s="3" t="s">
         <v>8</v>
@@ -3833,8 +4053,8 @@
       <c r="K91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="L91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -3845,9 +4065,12 @@
       <c r="O91" s="3">
         <v>0</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3887,9 +4110,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3929,51 +4155,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>855100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2950300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-4281700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-911800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-775900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2520800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1036600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-800500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-420000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1714800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2827600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1188700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1002100</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3990,50 +4222,54 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-601200</v>
+      </c>
+      <c r="E96" s="3">
         <v>-591500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-553900</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-546900</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-538400</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-510000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-501700</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-458400</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-446800</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-401700</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-301000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-186100</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-142900</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4073,9 +4309,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4115,9 +4354,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4157,133 +4399,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1454600</v>
+      </c>
+      <c r="E100" s="3">
         <v>2797900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>4873100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>13300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>876700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>2004700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1047700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>505500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-93300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1437500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>2640200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>986700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>809800</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>700</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>1100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>3200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-2700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-4400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-5800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>1100</v>
-      </c>
-      <c r="N101" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-70200</v>
+      </c>
+      <c r="E102" s="3">
         <v>60200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-400200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>148100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>86200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>69600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-232500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>258900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>88000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-62400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>140000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>63600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-112800</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/STWD_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/STWD_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="92">
   <si>
     <t>STWD</t>
   </si>
@@ -728,25 +728,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>2341200</v>
+        <v>370100</v>
       </c>
       <c r="E8" s="3">
-        <v>2220500</v>
+        <v>621200</v>
       </c>
       <c r="F8" s="3">
-        <v>1176500</v>
+        <v>717300</v>
       </c>
       <c r="G8" s="3">
-        <v>1136200</v>
+        <v>673000</v>
       </c>
       <c r="H8" s="3">
-        <v>1196400</v>
+        <v>677200</v>
       </c>
       <c r="I8" s="3">
-        <v>1109300</v>
+        <v>666200</v>
       </c>
       <c r="J8" s="3">
-        <v>879900</v>
+        <v>589700</v>
       </c>
       <c r="K8" s="3">
         <v>784700</v>
@@ -773,25 +773,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>1559600</v>
+        <v>45800</v>
       </c>
       <c r="E9" s="3">
-        <v>934000</v>
+        <v>47500</v>
       </c>
       <c r="F9" s="3">
-        <v>593400</v>
+        <v>112900</v>
       </c>
       <c r="G9" s="3">
-        <v>528900</v>
+        <v>121200</v>
       </c>
       <c r="H9" s="3">
-        <v>607600</v>
+        <v>124000</v>
       </c>
       <c r="I9" s="3">
-        <v>525100</v>
+        <v>135700</v>
       </c>
       <c r="J9" s="3">
-        <v>407900</v>
+        <v>97700</v>
       </c>
       <c r="K9" s="3">
         <v>348300</v>
@@ -818,25 +818,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>781500</v>
+        <v>324300</v>
       </c>
       <c r="E10" s="3">
-        <v>1286500</v>
+        <v>573700</v>
       </c>
       <c r="F10" s="3">
-        <v>583100</v>
+        <v>604400</v>
       </c>
       <c r="G10" s="3">
-        <v>607300</v>
+        <v>551800</v>
       </c>
       <c r="H10" s="3">
-        <v>588800</v>
+        <v>553200</v>
       </c>
       <c r="I10" s="3">
-        <v>584200</v>
+        <v>530500</v>
       </c>
       <c r="J10" s="3">
-        <v>471900</v>
+        <v>492000</v>
       </c>
       <c r="K10" s="3">
         <v>436400</v>
@@ -972,25 +972,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>127100</v>
+        <v>36900</v>
       </c>
       <c r="E14" s="3">
-        <v>4600</v>
+        <v>212000</v>
       </c>
       <c r="F14" s="3">
-        <v>8600</v>
+        <v>-100200</v>
       </c>
       <c r="G14" s="3">
-        <v>7200</v>
+        <v>-142200</v>
       </c>
       <c r="H14" s="3">
-        <v>21300</v>
+        <v>-241200</v>
       </c>
       <c r="I14" s="3">
-        <v>14800</v>
+        <v>-104100</v>
       </c>
       <c r="J14" s="3">
-        <v>10600</v>
+        <v>-77700</v>
       </c>
       <c r="K14" s="3">
         <v>22300</v>
@@ -1078,25 +1078,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2224500</v>
+        <v>415100</v>
       </c>
       <c r="E17" s="3">
-        <v>1274100</v>
+        <v>426800</v>
       </c>
       <c r="F17" s="3">
-        <v>996500</v>
+        <v>531300</v>
       </c>
       <c r="G17" s="3">
-        <v>968100</v>
+        <v>504400</v>
       </c>
       <c r="H17" s="3">
-        <v>1048800</v>
+        <v>515200</v>
       </c>
       <c r="I17" s="3">
-        <v>983400</v>
+        <v>544100</v>
       </c>
       <c r="J17" s="3">
-        <v>741300</v>
+        <v>467900</v>
       </c>
       <c r="K17" s="3">
         <v>660000</v>
@@ -1123,25 +1123,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>116700</v>
+        <v>-45000</v>
       </c>
       <c r="E18" s="3">
-        <v>946300</v>
+        <v>194300</v>
       </c>
       <c r="F18" s="3">
-        <v>180000</v>
+        <v>185900</v>
       </c>
       <c r="G18" s="3">
-        <v>168100</v>
+        <v>168600</v>
       </c>
       <c r="H18" s="3">
-        <v>147600</v>
+        <v>162000</v>
       </c>
       <c r="I18" s="3">
-        <v>125800</v>
+        <v>122100</v>
       </c>
       <c r="J18" s="3">
-        <v>138500</v>
+        <v>121700</v>
       </c>
       <c r="K18" s="3">
         <v>124700</v>
@@ -1187,25 +1187,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>300800</v>
+        <v>-208200</v>
       </c>
       <c r="E20" s="3">
-        <v>51200</v>
+        <v>-259500</v>
       </c>
       <c r="F20" s="3">
-        <v>321100</v>
+        <v>-208500</v>
       </c>
       <c r="G20" s="3">
-        <v>218200</v>
+        <v>-75500</v>
       </c>
       <c r="H20" s="3">
-        <v>402600</v>
+        <v>-147000</v>
       </c>
       <c r="I20" s="3">
-        <v>300700</v>
+        <v>-200400</v>
       </c>
       <c r="J20" s="3">
-        <v>305700</v>
+        <v>-244900</v>
       </c>
       <c r="K20" s="3">
         <v>251300</v>
@@ -1232,25 +1232,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>471800</v>
+        <v>212300</v>
       </c>
       <c r="E21" s="3">
-        <v>1051500</v>
+        <v>503100</v>
       </c>
       <c r="F21" s="3">
-        <v>585700</v>
+        <v>477500</v>
       </c>
       <c r="G21" s="3">
-        <v>480400</v>
+        <v>338500</v>
       </c>
       <c r="H21" s="3">
-        <v>663600</v>
+        <v>422300</v>
       </c>
       <c r="I21" s="3">
-        <v>557400</v>
+        <v>455100</v>
       </c>
       <c r="J21" s="3">
-        <v>535200</v>
+        <v>460200</v>
       </c>
       <c r="K21" s="3">
         <v>437600</v>
@@ -1276,26 +1276,26 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>15300</v>
       </c>
       <c r="J24" s="3">
-        <v>21200</v>
+        <v>31500</v>
       </c>
       <c r="K24" s="3">
         <v>8300</v>
@@ -1475,7 +1475,7 @@
         <v>411200</v>
       </c>
       <c r="J26" s="3">
-        <v>423100</v>
+        <v>412800</v>
       </c>
       <c r="K26" s="3">
         <v>367700</v>
@@ -1520,7 +1520,7 @@
         <v>382200</v>
       </c>
       <c r="J27" s="3">
-        <v>408000</v>
+        <v>397600</v>
       </c>
       <c r="K27" s="3">
         <v>363100</v>
@@ -1591,17 +1591,17 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>8</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
       </c>
       <c r="H29" s="3">
         <v>0</v>
@@ -1610,7 +1610,7 @@
         <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>-10400</v>
+        <v>0</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
@@ -1727,25 +1727,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-300800</v>
+        <v>208200</v>
       </c>
       <c r="E32" s="3">
-        <v>-51200</v>
+        <v>259500</v>
       </c>
       <c r="F32" s="3">
-        <v>-321100</v>
+        <v>208500</v>
       </c>
       <c r="G32" s="3">
-        <v>-218200</v>
+        <v>75500</v>
       </c>
       <c r="H32" s="3">
-        <v>-402600</v>
+        <v>147000</v>
       </c>
       <c r="I32" s="3">
-        <v>-300700</v>
+        <v>200400</v>
       </c>
       <c r="J32" s="3">
-        <v>-305700</v>
+        <v>244900</v>
       </c>
       <c r="K32" s="3">
         <v>-251300</v>
@@ -1772,25 +1772,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>332800</v>
+        <v>339200</v>
       </c>
       <c r="E33" s="3">
-        <v>854400</v>
+        <v>871500</v>
       </c>
       <c r="F33" s="3">
-        <v>440900</v>
+        <v>447700</v>
       </c>
       <c r="G33" s="3">
-        <v>326500</v>
+        <v>331700</v>
       </c>
       <c r="H33" s="3">
-        <v>505800</v>
+        <v>509700</v>
       </c>
       <c r="I33" s="3">
-        <v>382200</v>
+        <v>385800</v>
       </c>
       <c r="J33" s="3">
-        <v>397600</v>
+        <v>400800</v>
       </c>
       <c r="K33" s="3">
         <v>363100</v>
@@ -1862,25 +1862,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>332800</v>
+        <v>339200</v>
       </c>
       <c r="E35" s="3">
-        <v>854400</v>
+        <v>871500</v>
       </c>
       <c r="F35" s="3">
-        <v>440900</v>
+        <v>447700</v>
       </c>
       <c r="G35" s="3">
-        <v>326500</v>
+        <v>331700</v>
       </c>
       <c r="H35" s="3">
-        <v>505800</v>
+        <v>509700</v>
       </c>
       <c r="I35" s="3">
-        <v>382200</v>
+        <v>385800</v>
       </c>
       <c r="J35" s="3">
-        <v>397600</v>
+        <v>400800</v>
       </c>
       <c r="K35" s="3">
         <v>363100</v>
@@ -2040,25 +2040,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>63400</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>108600</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>48200</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>40600</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>28900</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>52700</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>33900</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -2085,25 +2085,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>200900</v>
+        <v>17775100</v>
       </c>
       <c r="E43" s="3">
-        <v>168500</v>
+        <v>18570000</v>
       </c>
       <c r="F43" s="3">
-        <v>116300</v>
+        <v>15653100</v>
       </c>
       <c r="G43" s="3">
-        <v>96000</v>
+        <v>11183100</v>
       </c>
       <c r="H43" s="3">
-        <v>64100</v>
+        <v>10650200</v>
       </c>
       <c r="I43" s="3">
-        <v>60400</v>
+        <v>8667100</v>
       </c>
       <c r="J43" s="3">
-        <v>47700</v>
+        <v>6684600</v>
       </c>
       <c r="K43" s="3">
         <v>28200</v>
@@ -2129,26 +2129,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2175,25 +2175,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
-      </c>
-      <c r="E45" s="3">
-        <v>0</v>
-      </c>
-      <c r="F45" s="3">
-        <v>0</v>
-      </c>
-      <c r="G45" s="3">
-        <v>0</v>
-      </c>
-      <c r="H45" s="3">
-        <v>0</v>
-      </c>
-      <c r="I45" s="3">
-        <v>0</v>
-      </c>
-      <c r="J45" s="3">
-        <v>0</v>
+        <v>290900</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -2220,25 +2220,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>21087100</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>21845300</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>18900000</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>12998600</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>12137300</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>10395200</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>7882600</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -2265,25 +2265,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>21045800</v>
+        <v>2838800</v>
       </c>
       <c r="E47" s="3">
-        <v>22093700</v>
+        <v>2668700</v>
       </c>
       <c r="F47" s="3">
-        <v>19364700</v>
+        <v>1991400</v>
       </c>
       <c r="G47" s="3">
-        <v>12984600</v>
+        <v>844700</v>
       </c>
       <c r="H47" s="3">
-        <v>12364800</v>
+        <v>894600</v>
       </c>
       <c r="I47" s="3">
-        <v>10872500</v>
+        <v>1078200</v>
       </c>
       <c r="J47" s="3">
-        <v>8286300</v>
+        <v>903700</v>
       </c>
       <c r="K47" s="3">
         <v>6958500</v>
@@ -2310,13 +2310,13 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>3059200</v>
+        <v>1046400</v>
       </c>
       <c r="E48" s="3">
-        <v>3211000</v>
+        <v>1450000</v>
       </c>
       <c r="F48" s="3">
-        <v>2206700</v>
+        <v>1166400</v>
       </c>
       <c r="G48" s="3">
         <v>2271200</v>
@@ -2490,25 +2490,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>117300</v>
+        <v>44148300</v>
       </c>
       <c r="E52" s="3">
-        <v>121100</v>
+        <v>52692900</v>
       </c>
       <c r="F52" s="3">
-        <v>104600</v>
+        <v>61469200</v>
       </c>
       <c r="G52" s="3">
-        <v>161900</v>
+        <v>64426200</v>
       </c>
       <c r="H52" s="3">
-        <v>109700</v>
+        <v>62384500</v>
       </c>
       <c r="I52" s="3">
-        <v>266200</v>
+        <v>53581100</v>
       </c>
       <c r="J52" s="3">
-        <v>48800</v>
+        <v>51164300</v>
       </c>
       <c r="K52" s="3">
         <v>35200</v>
@@ -2663,16 +2663,16 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>293400</v>
+        <v>244900</v>
       </c>
       <c r="E57" s="3">
-        <v>299000</v>
+        <v>289100</v>
       </c>
       <c r="F57" s="3">
-        <v>189700</v>
+        <v>176800</v>
       </c>
       <c r="G57" s="3">
-        <v>206800</v>
+        <v>200800</v>
       </c>
       <c r="H57" s="3">
         <v>212000</v>
@@ -2681,7 +2681,7 @@
         <v>217700</v>
       </c>
       <c r="J57" s="3">
-        <v>185100</v>
+        <v>178600</v>
       </c>
       <c r="K57" s="3">
         <v>198100</v>
@@ -2708,25 +2708,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1326200</v>
+        <v>107600</v>
       </c>
       <c r="E58" s="3">
-        <v>1874300</v>
+        <v>641400</v>
       </c>
       <c r="F58" s="3">
-        <v>2068300</v>
+        <v>13400</v>
       </c>
       <c r="G58" s="3">
-        <v>656700</v>
+        <v>41300</v>
       </c>
       <c r="H58" s="3">
-        <v>480200</v>
+        <v>8700</v>
       </c>
       <c r="I58" s="3">
-        <v>565200</v>
+        <v>89700</v>
       </c>
       <c r="J58" s="3">
-        <v>572900</v>
+        <v>110400</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>8</v>
@@ -2753,25 +2753,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>197700</v>
+        <v>152900</v>
       </c>
       <c r="E59" s="3">
-        <v>192700</v>
+        <v>151500</v>
       </c>
       <c r="F59" s="3">
-        <v>224000</v>
+        <v>147600</v>
       </c>
       <c r="G59" s="3">
-        <v>177100</v>
+        <v>138000</v>
       </c>
       <c r="H59" s="3">
-        <v>178400</v>
+        <v>137400</v>
       </c>
       <c r="I59" s="3">
-        <v>177500</v>
+        <v>133500</v>
       </c>
       <c r="J59" s="3">
-        <v>168300</v>
+        <v>125900</v>
       </c>
       <c r="K59" s="3">
         <v>162900</v>
@@ -2798,25 +2798,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>550200</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>1123200</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>414200</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>419200</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>399100</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>484800</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>457300</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -2843,25 +2843,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>18385600</v>
+        <v>19550700</v>
       </c>
       <c r="E61" s="3">
-        <v>18632700</v>
+        <v>19957000</v>
       </c>
       <c r="F61" s="3">
-        <v>14953300</v>
+        <v>17021600</v>
       </c>
       <c r="G61" s="3">
-        <v>12152500</v>
+        <v>12809300</v>
       </c>
       <c r="H61" s="3">
-        <v>11282500</v>
+        <v>11762700</v>
       </c>
       <c r="I61" s="3">
-        <v>10191400</v>
+        <v>10682400</v>
       </c>
       <c r="J61" s="3">
-        <v>7399600</v>
+        <v>7898300</v>
       </c>
       <c r="K61" s="3">
         <v>6200700</v>
@@ -2888,25 +2888,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>42380400</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
+        <v>50764200</v>
       </c>
       <c r="F62" s="3">
-        <v>0</v>
+        <v>59759800</v>
       </c>
       <c r="G62" s="3">
-        <v>0</v>
+        <v>62782400</v>
       </c>
       <c r="H62" s="3">
-        <v>0</v>
+        <v>60743500</v>
       </c>
       <c r="I62" s="3">
-        <v>0</v>
+        <v>52195000</v>
       </c>
       <c r="J62" s="3">
-        <v>0</v>
+        <v>50006500</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -3068,25 +3068,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>63253100</v>
+        <v>62481200</v>
       </c>
       <c r="E66" s="3">
-        <v>72580700</v>
+        <v>71844400</v>
       </c>
       <c r="F66" s="3">
-        <v>77777900</v>
+        <v>77201600</v>
       </c>
       <c r="G66" s="3">
-        <v>76384600</v>
+        <v>76010900</v>
       </c>
       <c r="H66" s="3">
-        <v>73341900</v>
+        <v>72905300</v>
       </c>
       <c r="I66" s="3">
-        <v>63659000</v>
+        <v>63362300</v>
       </c>
       <c r="J66" s="3">
-        <v>58462900</v>
+        <v>58362100</v>
       </c>
       <c r="K66" s="3">
         <v>72734000</v>
@@ -3632,25 +3632,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>332800</v>
+        <v>339200</v>
       </c>
       <c r="E81" s="3">
-        <v>854400</v>
+        <v>871500</v>
       </c>
       <c r="F81" s="3">
-        <v>440900</v>
+        <v>447700</v>
       </c>
       <c r="G81" s="3">
-        <v>326500</v>
+        <v>331700</v>
       </c>
       <c r="H81" s="3">
-        <v>505800</v>
+        <v>509700</v>
       </c>
       <c r="I81" s="3">
-        <v>382200</v>
+        <v>385800</v>
       </c>
       <c r="J81" s="3">
-        <v>397600</v>
+        <v>400800</v>
       </c>
       <c r="K81" s="3">
         <v>363100</v>
@@ -3696,10 +3696,10 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>54300</v>
+        <v>45600</v>
       </c>
       <c r="E83" s="3">
-        <v>53900</v>
+        <v>45100</v>
       </c>
       <c r="F83" s="3">
         <v>84600</v>
@@ -4030,25 +4030,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-25100</v>
       </c>
       <c r="E91" s="3">
-        <v>0</v>
+        <v>-25200</v>
       </c>
       <c r="F91" s="3">
-        <v>-28100</v>
-      </c>
-      <c r="G91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J91" s="3" t="s">
-        <v>8</v>
+        <v>-26300</v>
+      </c>
+      <c r="G91" s="3">
+        <v>-25200</v>
+      </c>
+      <c r="H91" s="3">
+        <v>-30900</v>
+      </c>
+      <c r="I91" s="3">
+        <v>-54800</v>
+      </c>
+      <c r="J91" s="3">
+        <v>-573900</v>
       </c>
       <c r="K91" s="3" t="s">
         <v>8</v>
@@ -4229,25 +4229,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-601200</v>
+        <v>601200</v>
       </c>
       <c r="E96" s="3">
-        <v>-591500</v>
+        <v>591500</v>
       </c>
       <c r="F96" s="3">
-        <v>-553900</v>
+        <v>553900</v>
       </c>
       <c r="G96" s="3">
-        <v>-546900</v>
+        <v>546900</v>
       </c>
       <c r="H96" s="3">
-        <v>-538400</v>
+        <v>538400</v>
       </c>
       <c r="I96" s="3">
-        <v>-510000</v>
+        <v>510000</v>
       </c>
       <c r="J96" s="3">
-        <v>-501700</v>
+        <v>501700</v>
       </c>
       <c r="K96" s="3">
         <v>-458400</v>

--- a/AAII_Financials/Yearly/STWD_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/STWD_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="92">
   <si>
     <t>STWD</t>
   </si>
@@ -656,209 +656,221 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41274</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40908</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>400800</v>
+      </c>
+      <c r="E8" s="3">
         <v>370100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>621200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>717300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>673000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>677200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>666200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>589700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>784700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>735900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>702900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>549500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>307300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>206500</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>45800</v>
+        <v>48200</v>
       </c>
       <c r="E9" s="3">
-        <v>47500</v>
+        <v>44800</v>
       </c>
       <c r="F9" s="3">
+        <v>44100</v>
+      </c>
+      <c r="G9" s="3">
         <v>112900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>121200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>124000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>135700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>97700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>348300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>327300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>278800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>188600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>104400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>68000</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>324300</v>
+        <v>352500</v>
       </c>
       <c r="E10" s="3">
-        <v>573700</v>
+        <v>325200</v>
       </c>
       <c r="F10" s="3">
+        <v>577100</v>
+      </c>
+      <c r="G10" s="3">
         <v>604400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>551800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>553200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>530500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>492000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>436400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>408600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>424000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>360900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>202900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>138500</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -876,8 +888,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -920,9 +933,12 @@
       <c r="P12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -965,99 +981,108 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-173700</v>
+      </c>
+      <c r="E14" s="3">
         <v>36900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>212000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-100200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-142200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-241200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-104100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-77700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>22300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>19400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>5500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>23700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>10700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>11000</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>41300</v>
+      </c>
+      <c r="E15" s="3">
         <v>49100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>49300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>83000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>94400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>113300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>132600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>93600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>66800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>29000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>16600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>9700</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1072,98 +1097,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>415100</v>
+        <v>431000</v>
       </c>
       <c r="E17" s="3">
-        <v>426800</v>
+        <v>414100</v>
       </c>
       <c r="F17" s="3">
+        <v>423400</v>
+      </c>
+      <c r="G17" s="3">
         <v>531300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>504400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>515200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>544100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>467900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>660000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>542200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>485800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>375200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>129000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>87700</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-45000</v>
+        <v>-30200</v>
       </c>
       <c r="E18" s="3">
-        <v>194300</v>
+        <v>-44100</v>
       </c>
       <c r="F18" s="3">
+        <v>197700</v>
+      </c>
+      <c r="G18" s="3">
         <v>185900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>168600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>162000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>122100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>121700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>124700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>193700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>217100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>174300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>178300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>118700</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1181,98 +1213,105 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-208200</v>
+        <v>-160400</v>
       </c>
       <c r="E20" s="3">
-        <v>-259500</v>
+        <v>-207200</v>
       </c>
       <c r="F20" s="3">
+        <v>-256100</v>
+      </c>
+      <c r="G20" s="3">
         <v>-208500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-75500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-147000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-200400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-244900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>251300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>275700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>309100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>179700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>28300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>2700</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>171500</v>
+      </c>
+      <c r="E21" s="3">
         <v>212300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>503100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>477500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>338500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>422300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>455100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>460200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>437600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>496600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>542800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>368900</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1297,8 +1336,8 @@
       <c r="J22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1315,99 +1354,108 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>406000</v>
+      </c>
+      <c r="E23" s="3">
         <v>417500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>997500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>501100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>386300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>550200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>426500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>444300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>376000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>469400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>526200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>354000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>206600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>121400</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>25400</v>
+      </c>
+      <c r="E24" s="3">
         <v>-700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-61500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>8700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>20200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>13200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>15300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>31500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>8300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>17200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>24100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>23900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>800</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1450,99 +1498,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>380600</v>
+      </c>
+      <c r="E26" s="3">
         <v>418200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1059100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>492400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>366100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>536900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>411200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>412800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>367700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>452200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>502100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>330100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>205700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>120600</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>352700</v>
+      </c>
+      <c r="E27" s="3">
         <v>332800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>854400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>440900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>326500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>505800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>382200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>397600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>363100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>447300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>491000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>323200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>201600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>117200</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1585,9 +1642,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1619,20 +1679,23 @@
         <v>0</v>
       </c>
       <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>-1600</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-19800</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-2000</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1675,9 +1738,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1720,99 +1786,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>208200</v>
+        <v>160400</v>
       </c>
       <c r="E32" s="3">
-        <v>259500</v>
+        <v>207200</v>
       </c>
       <c r="F32" s="3">
+        <v>256100</v>
+      </c>
+      <c r="G32" s="3">
         <v>208500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>75500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>147000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>200400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>244900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-251300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-275700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-309100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-179700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-28300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>359900</v>
+      </c>
+      <c r="E33" s="3">
         <v>339200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>871500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>447700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>331700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>509700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>385800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>400800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>363100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>447300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>489400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>303500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>199600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>117200</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1855,104 +1930,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>359900</v>
+      </c>
+      <c r="E35" s="3">
         <v>339200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>871500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>447700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>331700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>509700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>385800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>400800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>363100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>447300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>489400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>303500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>199600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>117200</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41274</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40908</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1970,8 +2054,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1989,80 +2074,84 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>377800</v>
+      </c>
+      <c r="E41" s="3">
         <v>194700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>261100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>217400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>563200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>478400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>239800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>369400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>615500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>368800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>255200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>317600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>177700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>114000</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>175500</v>
+      </c>
+      <c r="E42" s="3">
         <v>63400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>108600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>48200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>40600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>28900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>52700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>33900</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
@@ -2078,54 +2167,60 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>15604800</v>
+      </c>
+      <c r="E43" s="3">
         <v>17775100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>18570000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>15653100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>11183100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>10650200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>8667100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>6684600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>28200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>34300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>40100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>37600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>24100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>15200</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2150,8 +2245,8 @@
       <c r="J44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2168,18 +2263,21 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3">
         <v>290900</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="F45" s="3" t="s">
         <v>8</v>
       </c>
@@ -2195,8 +2293,8 @@
       <c r="J45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
+      <c r="K45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L45" s="3">
         <v>0</v>
@@ -2213,36 +2311,39 @@
       <c r="P45" s="3">
         <v>0</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3">
+        <v>0</v>
+      </c>
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>18850300</v>
+      </c>
+      <c r="E46" s="3">
         <v>21087100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>21845300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>18900000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>12998600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>12137300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>10395200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>7882600</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -2258,87 +2359,93 @@
       <c r="P46" s="3">
         <v>0</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3">
+        <v>0</v>
+      </c>
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2706200</v>
+      </c>
+      <c r="E47" s="3">
         <v>2838800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2668700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1991400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>844700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>894600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1078200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>903700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>6958500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>7187700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>7492500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>6773400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>4084900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2833600</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1373700</v>
+      </c>
+      <c r="E48" s="3">
         <v>1046400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1450000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1166400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2271200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2266400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2784900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2647500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1944700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>919200</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>8</v>
       </c>
@@ -2348,54 +2455,60 @@
       <c r="P48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>320600</v>
+      </c>
+      <c r="E49" s="3">
         <v>324800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>328600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>323400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>330000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>345500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>404900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>323500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>359700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>342000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>284600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>317600</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2438,9 +2551,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2483,54 +2599,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>39268800</v>
+      </c>
+      <c r="E52" s="3">
         <v>44148300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>52692900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>61469200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>64426200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>62384500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>53581100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>51164300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>35200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>23100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>48700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>69100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3400</v>
       </c>
-      <c r="P52" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2573,54 +2695,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>62556500</v>
+      </c>
+      <c r="E54" s="3">
         <v>69504200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>79043100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>83850400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>80873500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>78042300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>68262500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>62941300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>77256300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>85698400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>116099000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>110771000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4324400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2997400</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2638,8 +2766,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2657,80 +2786,84 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>244900</v>
+        <v>367500</v>
       </c>
       <c r="E57" s="3">
+        <v>282500</v>
+      </c>
+      <c r="F57" s="3">
         <v>289100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>176800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>200800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>212000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>217700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>178600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>198100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>156800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>144500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>225400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>8900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>13400</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>107600</v>
+        <v>350200</v>
       </c>
       <c r="E58" s="3">
+        <v>502500</v>
+      </c>
+      <c r="F58" s="3">
         <v>641400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>13400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>41300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>8700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>89700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>110400</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L58" s="3" t="s">
         <v>8</v>
       </c>
@@ -2746,81 +2879,87 @@
       <c r="P58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>152900</v>
+        <v>163400</v>
       </c>
       <c r="E59" s="3">
+        <v>346600</v>
+      </c>
+      <c r="F59" s="3">
         <v>151500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>147600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>138000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>137400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>133500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>125900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>162900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>155900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>148900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>108000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>75600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>41400</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>550200</v>
+        <v>920100</v>
       </c>
       <c r="E60" s="3">
+        <v>1176400</v>
+      </c>
+      <c r="F60" s="3">
         <v>1123200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>414200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>419200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>399100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>484800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>457300</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -2836,81 +2975,87 @@
       <c r="P60" s="3">
         <v>0</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3">
+        <v>0</v>
+      </c>
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>19550700</v>
+        <v>17122900</v>
       </c>
       <c r="E61" s="3">
+        <v>19118200</v>
+      </c>
+      <c r="F61" s="3">
         <v>19957000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>17021600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>12809300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>11762700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>10682400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>7898300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>6200700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5392500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4685300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3436600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1393700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1156700</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>42380400</v>
+        <v>37320100</v>
       </c>
       <c r="E62" s="3">
+        <v>42186700</v>
+      </c>
+      <c r="F62" s="3">
         <v>50764200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>59759800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>62782400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>60743500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>52195000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>50006500</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
       <c r="L62" s="3">
         <v>0</v>
       </c>
@@ -2926,9 +3071,12 @@
       <c r="P62" s="3">
         <v>0</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3">
+        <v>0</v>
+      </c>
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2971,9 +3119,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3016,9 +3167,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3061,54 +3215,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>55363000</v>
+      </c>
+      <c r="E66" s="3">
         <v>62481200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>71844400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>77201600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>76010900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>72905300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>63362300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>58362100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>72734000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>81558000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>112238000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>106488000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1605000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1238000</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3126,8 +3286,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3170,9 +3331,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3215,9 +3379,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3260,9 +3427,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3305,54 +3475,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>235300</v>
+      </c>
+      <c r="E72" s="3">
         <v>505900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>769200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>493100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-629700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-381700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-349000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-217300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-115600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-12300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-9400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-84700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-72400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-55100</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3395,9 +3571,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3440,9 +3619,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3485,54 +3667,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6437100</v>
+      </c>
+      <c r="E76" s="3">
         <v>6251100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>6462400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6072500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4488900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4700400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4603400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4478400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4522300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4140300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3860900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4282500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2719300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1759500</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3575,104 +3763,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41274</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40908</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>359900</v>
+      </c>
+      <c r="E81" s="3">
         <v>339200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>871500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>447700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>331700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>509700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>385800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>400800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>363100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>447300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>489400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>303500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>199600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>117200</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3690,53 +3887,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>39000</v>
+      </c>
+      <c r="E83" s="3">
         <v>45600</v>
       </c>
-      <c r="E83" s="3">
-        <v>45100</v>
-      </c>
       <c r="F83" s="3">
+        <v>53900</v>
+      </c>
+      <c r="G83" s="3">
         <v>84600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>94200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>113400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>130800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>90900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>61600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>27200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>16600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>14900</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3779,9 +3980,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3824,9 +4028,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3869,9 +4076,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3914,9 +4124,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3959,54 +4172,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>646600</v>
+      </c>
+      <c r="E89" s="3">
         <v>528600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>213700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-990000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1045500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-13200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>585500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-246800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>556600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>605700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>220700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>326300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>265600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>79400</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4024,40 +4243,41 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-27900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-25100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-25200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-26300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-25200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-30900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-54800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-573900</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
+      <c r="M91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -4068,9 +4288,12 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4113,9 +4336,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4158,54 +4384,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>2084000</v>
+      </c>
+      <c r="E94" s="3">
         <v>855100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2950300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-4281700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-911800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-775900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2520800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1036600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-800500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-420000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1714800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2827600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1188700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1002100</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4223,53 +4455,57 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>620000</v>
+      </c>
+      <c r="E96" s="3">
         <v>601200</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>591500</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>553900</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>546900</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>538400</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>510000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>501700</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-458400</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-446800</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-401700</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-301000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-186100</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-142900</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4312,9 +4548,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4357,9 +4596,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4402,142 +4644,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2485900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1454600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2797900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>4873100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>13300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>876700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>2004700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1047700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>505500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-93300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1437500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>2640200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>986700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>809800</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E101" s="3">
         <v>700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>3200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-2700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-4400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-5800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>1100</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>242000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-70200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>60200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-400200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>148100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>86200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>69600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-232500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>258900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>88000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-62400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>140000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>63600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-112800</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/STWD_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/STWD_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="92">
   <si>
     <t>STWD</t>
   </si>
@@ -656,221 +656,233 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41274</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40908</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>547900</v>
+      </c>
+      <c r="E8" s="3">
         <v>400800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>370100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>621200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>717300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>673000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>677200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>666200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>589700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>784700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>735900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>702900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>549500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>307300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>206500</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>60800</v>
+      </c>
+      <c r="E9" s="3">
         <v>48200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>44800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>44100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>112900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>121200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>124000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>135700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>97700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>348300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>327300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>278800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>188600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>104400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>68000</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>487100</v>
+      </c>
+      <c r="E10" s="3">
         <v>352500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>325200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>577100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>604400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>551800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>553200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>530500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>492000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>436400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>408600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>424000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>360900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>202900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>138500</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -889,8 +901,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -936,9 +949,12 @@
       <c r="Q12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -984,105 +1000,114 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-220500</v>
+      </c>
+      <c r="E14" s="3">
         <v>-173700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>36900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>212000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-100200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-142200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-241200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-104100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-77700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>22300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>19400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>5500</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>23700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>10700</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>11000</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>79000</v>
+      </c>
+      <c r="E15" s="3">
         <v>41300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>49100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>49300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>83000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>94400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>113300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>132600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>93600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>66800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>29000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>16600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>9700</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1098,104 +1123,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>480000</v>
+      </c>
+      <c r="E17" s="3">
         <v>431000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>414100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>423400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>531300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>504400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>515200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>544100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>467900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>660000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>542200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>485800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>375200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>129000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>87700</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>68000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-30200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-44100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>197700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>185900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>168600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>162000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>122100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>121700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>124700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>193700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>217100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>174300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>178300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>118700</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1214,104 +1246,111 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-144400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-160400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-207200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-256100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-208500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-75500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-147000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-200400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-244900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>251300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>275700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>309100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>179700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>28300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>2700</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>291400</v>
+      </c>
+      <c r="E21" s="3">
         <v>171500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>212300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>503100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>477500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>338500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>422300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>455100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>460200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>437600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>496600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>542800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>368900</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1339,8 +1378,8 @@
       <c r="K22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1357,105 +1396,114 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>479800</v>
+      </c>
+      <c r="E23" s="3">
         <v>406000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>417500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>997500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>501100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>386300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>550200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>426500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>444300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>376000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>469400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>526200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>354000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>206600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>121400</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>36700</v>
+      </c>
+      <c r="E24" s="3">
         <v>25400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-61500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>8700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>20200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>13200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>15300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>31500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>8300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>17200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>24100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>23900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>800</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1501,105 +1549,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>443100</v>
+      </c>
+      <c r="E26" s="3">
         <v>380600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>418200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1059100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>492400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>366100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>536900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>411200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>412800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>367700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>452200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>502100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>330100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>205700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>120600</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>402400</v>
+      </c>
+      <c r="E27" s="3">
         <v>352700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>332800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>854400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>440900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>326500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>505800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>382200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>397600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>363100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>447300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>491000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>323200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>201600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>117200</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1645,9 +1702,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1682,20 +1742,23 @@
         <v>0</v>
       </c>
       <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
         <v>-1600</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-19800</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1741,9 +1804,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1789,105 +1855,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>144400</v>
+      </c>
+      <c r="E32" s="3">
         <v>160400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>207200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>256100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>208500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>75500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>147000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>200400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>244900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-251300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-275700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-309100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-179700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-28300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-2700</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>411500</v>
+      </c>
+      <c r="E33" s="3">
         <v>359900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>339200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>871500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>447700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>331700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>509700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>385800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>400800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>363100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>447300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>489400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>303500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>199600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>117200</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1933,110 +2008,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>411500</v>
+      </c>
+      <c r="E35" s="3">
         <v>359900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>339200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>871500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>447700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>331700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>509700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>385800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>400800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>363100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>447300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>489400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>303500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>199600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>117200</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41274</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40908</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2055,8 +2139,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2075,86 +2160,90 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>499500</v>
+      </c>
+      <c r="E41" s="3">
         <v>377800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>194700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>261100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>217400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>563200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>478400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>239800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>369400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>615500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>368800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>255200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>317600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>177700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>114000</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>45800</v>
+      </c>
+      <c r="E42" s="3">
         <v>175500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>63400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>108600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>48200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>40600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>28900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>52700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>33900</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -2170,57 +2259,63 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>19027200</v>
+      </c>
+      <c r="E43" s="3">
         <v>15604800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>17775100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>18570000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>15653100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>11183100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>10650200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>8667100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>6684600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>28200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>34300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>40100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>37600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>24100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>15200</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2248,8 +2343,8 @@
       <c r="K44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2266,21 +2361,24 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="3">
         <v>290900</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G45" s="3" t="s">
         <v>8</v>
       </c>
@@ -2296,8 +2394,8 @@
       <c r="K45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
+      <c r="L45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M45" s="3">
         <v>0</v>
@@ -2314,39 +2412,42 @@
       <c r="Q45" s="3">
         <v>0</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R45" s="3">
+        <v>0</v>
+      </c>
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>22071200</v>
+      </c>
+      <c r="E46" s="3">
         <v>18850300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>21087100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>21845300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>18900000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>12998600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>12137300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>10395200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>7882600</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -2362,93 +2463,99 @@
       <c r="Q46" s="3">
         <v>0</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R46" s="3">
+        <v>0</v>
+      </c>
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2113300</v>
+      </c>
+      <c r="E47" s="3">
         <v>2706200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2838800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2668700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1991400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>844700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>894600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1078200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>903700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>6958500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>7187700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>7492500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>6773400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>4084900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2833600</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3516700</v>
+      </c>
+      <c r="E48" s="3">
         <v>1373700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1046400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1450000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1166400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2271200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2266400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2784900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2647500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1944700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>919200</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>8</v>
       </c>
@@ -2458,57 +2565,63 @@
       <c r="Q48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>695900</v>
+      </c>
+      <c r="E49" s="3">
         <v>320600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>324800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>328600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>323400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>330000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>345500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>404900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>323500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>359700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>342000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>284600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>317600</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2554,9 +2667,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2602,57 +2718,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>34780800</v>
+      </c>
+      <c r="E52" s="3">
         <v>39268800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>44148300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>52692900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>61469200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>64426200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>62384500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>53581100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>51164300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>35200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>23100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>48700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>69100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3400</v>
       </c>
-      <c r="Q52" s="3">
-        <v>0</v>
-      </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R52" s="3">
+        <v>0</v>
+      </c>
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2698,57 +2820,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>63183400</v>
+      </c>
+      <c r="E54" s="3">
         <v>62556500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>69504200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>79043100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>83850400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>80873500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>78042300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>68262500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>62941300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>77256300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>85698400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>116099000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>110771000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4324400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2997400</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2767,8 +2895,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2787,86 +2916,90 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>367500</v>
+        <v>353200</v>
       </c>
       <c r="E57" s="3">
+        <v>402000</v>
+      </c>
+      <c r="F57" s="3">
         <v>282500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>289100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>176800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>200800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>212000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>217700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>178600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>198100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>156800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>144500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>225400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>8900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>13400</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>350200</v>
+        <v>1490700</v>
       </c>
       <c r="E58" s="3">
+        <v>344900</v>
+      </c>
+      <c r="F58" s="3">
         <v>502500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>641400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>13400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>41300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>8700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>89700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>110400</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>8</v>
       </c>
@@ -2882,87 +3015,93 @@
       <c r="Q58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>183100</v>
+      </c>
+      <c r="E59" s="3">
         <v>163400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>346600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>151500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>147600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>138000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>137400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>133500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>125900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>162900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>155900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>148900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>108000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>75600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>41400</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>920100</v>
+        <v>2058700</v>
       </c>
       <c r="E60" s="3">
+        <v>949200</v>
+      </c>
+      <c r="F60" s="3">
         <v>1176400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1123200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>414200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>419200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>399100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>484800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>457300</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -2978,87 +3117,93 @@
       <c r="Q60" s="3">
         <v>0</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R60" s="3">
+        <v>0</v>
+      </c>
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>17122900</v>
+        <v>20756600</v>
       </c>
       <c r="E61" s="3">
+        <v>17092700</v>
+      </c>
+      <c r="F61" s="3">
         <v>19118200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>19957000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>17021600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>12809300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>11762700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>10682400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>7898300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>6200700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5392500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4685300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3436600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1393700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1156700</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>37320100</v>
+        <v>32878600</v>
       </c>
       <c r="E62" s="3">
+        <v>37321200</v>
+      </c>
+      <c r="F62" s="3">
         <v>42186700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>50764200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>59759800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>62782400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>60743500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>52195000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>50006500</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
-      </c>
       <c r="M62" s="3">
         <v>0</v>
       </c>
@@ -3074,9 +3219,12 @@
       <c r="Q62" s="3">
         <v>0</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R62" s="3">
+        <v>0</v>
+      </c>
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3122,9 +3270,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3170,9 +3321,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3218,57 +3372,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>55693900</v>
+      </c>
+      <c r="E66" s="3">
         <v>55363000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>62481200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>71844400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>77201600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>76010900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>72905300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>63362300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>58362100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>72734000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>81558000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>112238000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>106488000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1605000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1238000</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3287,8 +3447,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3334,9 +3495,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3382,9 +3546,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3430,9 +3597,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3478,57 +3648,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-39000</v>
+      </c>
+      <c r="E72" s="3">
         <v>235300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>505900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>769200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>493100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-629700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-381700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-349000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-217300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-115600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-12300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-9400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-84700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-72400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-55100</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3574,9 +3750,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3622,9 +3801,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3670,57 +3852,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6795500</v>
+      </c>
+      <c r="E76" s="3">
         <v>6437100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>6251100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6462400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>6072500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4488900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4700400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4603400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4478400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4522300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4140300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3860900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4282500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2719300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1759500</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3766,110 +3954,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41274</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40908</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>411500</v>
+      </c>
+      <c r="E81" s="3">
         <v>359900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>339200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>871500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>447700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>331700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>509700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>385800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>400800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>363100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>447300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>489400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>303500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>199600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>117200</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3888,56 +4085,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>39000</v>
+        <v>70900</v>
       </c>
       <c r="E83" s="3">
-        <v>45600</v>
+        <v>39300</v>
       </c>
       <c r="F83" s="3">
+        <v>54300</v>
+      </c>
+      <c r="G83" s="3">
         <v>53900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>84600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>94200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>113400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>130800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>90900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>61600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>27200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>16600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>14900</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3983,9 +4184,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4031,9 +4235,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4079,9 +4286,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4127,9 +4337,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4175,57 +4388,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>977900</v>
+      </c>
+      <c r="E89" s="3">
         <v>646600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>528600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>213700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-990000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1045500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-13200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>585500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-246800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>556600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>605700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>220700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>326300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>265600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>79400</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4244,43 +4463,44 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-269000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-27900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-25100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-25200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-26300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-25200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-30900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-54800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-573900</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
+      <c r="N91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O91" s="3">
         <v>0</v>
@@ -4291,9 +4511,12 @@
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4339,9 +4562,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4387,57 +4613,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3776500</v>
+      </c>
+      <c r="E94" s="3">
         <v>2084000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>855100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2950300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-4281700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-911800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-775900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2520800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1036600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-800500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-420000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1714800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2827600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1188700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1002100</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4456,56 +4688,60 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>668900</v>
+      </c>
+      <c r="E96" s="3">
         <v>620000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>601200</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>591500</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>553900</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>546900</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>538400</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>510000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>501700</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-458400</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-446800</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-401700</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-301000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-186100</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-142900</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4551,9 +4787,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4599,9 +4838,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4647,151 +4889,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2919600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2485900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1454600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2797900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>4873100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>13300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>876700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>2004700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1047700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>505500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-93300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1437500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>2640200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>986700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>809800</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E101" s="3">
         <v>-2600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>1100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>3200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-2700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-4400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-5800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>1100</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>120700</v>
+      </c>
+      <c r="E102" s="3">
         <v>242000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-70200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>60200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-400200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>148100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>86200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>69600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-232500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>258900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>88000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-62400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>140000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>63600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-112800</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
